--- a/docs/CodeSystem-underwater-communication-cs.xlsx
+++ b/docs/CodeSystem-underwater-communication-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-underwater-communication-cs.xlsx
+++ b/docs/CodeSystem-underwater-communication-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-underwater-communication-cs.xlsx
+++ b/docs/CodeSystem-underwater-communication-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-underwater-communication-cs.xlsx
+++ b/docs/CodeSystem-underwater-communication-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-underwater-communication-cs.xlsx
+++ b/docs/CodeSystem-underwater-communication-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/CodeSystem/underwater-communication-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/underwater-communication-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,12 +93,12 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>31</t>
   </si>
   <si>
     <t>Level</t>
@@ -310,6 +310,114 @@
   </si>
   <si>
     <t>Testing effective communication range</t>
+  </si>
+  <si>
+    <t>comm-range</t>
+  </si>
+  <si>
+    <t>Communication Range</t>
+  </si>
+  <si>
+    <t>Device property type: maximum effective communication range of the system</t>
+  </si>
+  <si>
+    <t>encryption</t>
+  </si>
+  <si>
+    <t>Encryption Capability</t>
+  </si>
+  <si>
+    <t>Device property type: whether the system supports encrypted communication</t>
+  </si>
+  <si>
+    <t>battery-life</t>
+  </si>
+  <si>
+    <t>Battery Life</t>
+  </si>
+  <si>
+    <t>Device property type: rated operating time on a full battery charge</t>
+  </si>
+  <si>
+    <t>waterproof-rating</t>
+  </si>
+  <si>
+    <t>Waterproof Rating</t>
+  </si>
+  <si>
+    <t>Device property type: ingress protection or depth rating of the housing</t>
+  </si>
+  <si>
+    <t>operating-depth</t>
+  </si>
+  <si>
+    <t>Operating Depth</t>
+  </si>
+  <si>
+    <t>Device property type: maximum rated operating depth of the system</t>
+  </si>
+  <si>
+    <t>comm-assessment</t>
+  </si>
+  <si>
+    <t>Communication Assessment</t>
+  </si>
+  <si>
+    <t>Assessment of communication system performance during a training session</t>
+  </si>
+  <si>
+    <t>signal-strength</t>
+  </si>
+  <si>
+    <t>Signal Strength</t>
+  </si>
+  <si>
+    <t>Measured signal strength of the communication link</t>
+  </si>
+  <si>
+    <t>audio-clarity</t>
+  </si>
+  <si>
+    <t>Audio Clarity</t>
+  </si>
+  <si>
+    <t>Assessed clarity and intelligibility of voice communication</t>
+  </si>
+  <si>
+    <t>comm-reliability</t>
+  </si>
+  <si>
+    <t>Communication Reliability</t>
+  </si>
+  <si>
+    <t>Percentage of the session during which communication was maintained</t>
+  </si>
+  <si>
+    <t>emergency-response-time</t>
+  </si>
+  <si>
+    <t>Emergency Communication Response Time</t>
+  </si>
+  <si>
+    <t>Time from emergency signal to acknowledged response</t>
+  </si>
+  <si>
+    <t>security-assessment</t>
+  </si>
+  <si>
+    <t>Security Assessment</t>
+  </si>
+  <si>
+    <t>Assessment of the security and integrity of the communication link</t>
+  </si>
+  <si>
+    <t>communication-log</t>
+  </si>
+  <si>
+    <t>Communication Log</t>
+  </si>
+  <si>
+    <t>Narrative log of communications during the dive</t>
   </si>
 </sst>
 </file>
@@ -556,14 +664,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -619,7 +729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -902,6 +1012,174 @@
         <v>98</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
